--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612459.8386321691</v>
+        <v>612460</v>
       </c>
       <c r="R2" t="n">
-        <v>6767032.696605737</v>
+        <v>6767033</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2004-08-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612459.8386321691</v>
+        <v>612460</v>
       </c>
       <c r="R3" t="n">
-        <v>6767032.696605737</v>
+        <v>6767033</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,19 +859,9 @@
           <t>2004-08-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-08-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,12 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612459.8386321691</v>
+        <v>612460</v>
       </c>
       <c r="R4" t="n">
-        <v>6767032.696605737</v>
+        <v>6767033</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,19 +975,9 @@
           <t>2004-08-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2004-08-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1071,12 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612459.8386321691</v>
+        <v>612460</v>
       </c>
       <c r="R5" t="n">
-        <v>6767032.696605737</v>
+        <v>6767033</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,19 +1091,9 @@
           <t>2004-08-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2004-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1202,12 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612405.7237388436</v>
+        <v>612406</v>
       </c>
       <c r="R6" t="n">
-        <v>6766962.09527201</v>
+        <v>6766962</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1277,19 +1212,9 @@
           <t>2000-09-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2000-09-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1338,12 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612356.5456539978</v>
+        <v>612357</v>
       </c>
       <c r="R7" t="n">
-        <v>6766904.262752797</v>
+        <v>6766904</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1413,19 +1333,9 @@
           <t>2000-09-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2000-09-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1474,12 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612405.7237388436</v>
+        <v>612406</v>
       </c>
       <c r="R8" t="n">
-        <v>6766962.09527201</v>
+        <v>6766962</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1549,19 +1454,9 @@
           <t>2000-09-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2000-09-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1610,12 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1647,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612451.8103897221</v>
+        <v>612452</v>
       </c>
       <c r="R9" t="n">
-        <v>6766979.567601576</v>
+        <v>6766980</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1685,19 +1575,9 @@
           <t>2000-09-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2000-09-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1741,12 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612356.5456539978</v>
+        <v>612357</v>
       </c>
       <c r="R10" t="n">
-        <v>6766904.262752797</v>
+        <v>6766904</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1816,19 +1691,9 @@
           <t>2000-09-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2000-09-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1877,12 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1914,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>612356.5456539978</v>
+        <v>612357</v>
       </c>
       <c r="R11" t="n">
-        <v>6766904.262752797</v>
+        <v>6766904</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1952,19 +1812,9 @@
           <t>2000-09-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2000-09-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35647-2025 artfynd.xlsx
+++ b/artfynd/A 35647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91299283</v>
       </c>
       <c r="B2" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>91299278</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>91299281</v>
       </c>
       <c r="B4" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>91299276</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>92074066</v>
       </c>
       <c r="B6" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>92074100</v>
       </c>
       <c r="B7" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>92074064</v>
       </c>
       <c r="B8" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>92074004</v>
       </c>
       <c r="B9" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>92074106</v>
       </c>
       <c r="B10" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>92074102</v>
       </c>
       <c r="B11" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
